--- a/kelly_criterion.xlsx
+++ b/kelly_criterion.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F91814D663B1EE2BBFD8C07F5FB8D320D8ABD053" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF900944-EADA-4B73-B6FB-3958FB27CF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kelly Criterion" sheetId="1" r:id="rId1"/>
+    <sheet name="Monte Carlo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Kelly Criterion Calculator</t>
   </si>
@@ -130,6 +131,45 @@
   </si>
   <si>
     <t>Grid recomputes f* for each combination of win probability (rows) and payout ratio (columns). Independent of the single-scenario inputs above.</t>
+  </si>
+  <si>
+    <t>Monte Carlo Simulation</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORM.INV =&gt; Normalverteilung: Umkehr der kumulativen Verteilung </t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>randbetween =&gt; gleichverteilung (ganzzahlig)</t>
+  </si>
+  <si>
+    <t>lower_limit =&gt; gleichverteilung (kontinuierlich)</t>
+  </si>
+  <si>
+    <t>NORMAL.DIST =&gt; Normalverteilung kumulativ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BINOM.DIST =&gt; Binomale Verteilung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poisson.DIST =&gt; Poisson Verteilung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPON.DIST =&gt; exponentielle Verteilung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamma.DIST =&gt; Gamma Verteilung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta:DIST =&gt; Beta Verteilung </t>
+  </si>
+  <si>
+    <t>f9</t>
   </si>
 </sst>
 </file>
@@ -141,13 +181,19 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -198,6 +244,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -243,35 +303,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1065,610 +1131,610 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="3">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="4">
         <f>1-B5</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="6">
         <f>B7*B5-B6</f>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <f>MAX((B7*B5-B6)/B7,0)</f>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="4">
         <f>B11/2</f>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="4">
         <f>B11/4</f>
         <v>2.5000000000000022E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="8">
         <f>B5*LN(1+B7*B11)+B6*LN(1-B11)</f>
         <v>5.008366846356839E-3</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="9">
         <f>IF(B14&gt;0,LN(2)/B14,"n/a")</f>
         <v>138.39784541025602</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+      <c r="A21" s="10">
         <v>0</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="8">
         <f>B5*LN(1+B7*A21)+B6*LN(1-A21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+      <c r="A22" s="10">
         <v>0.05</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="8">
         <f>B5*LN(1+B7*A22)+B6*LN(1-A22)</f>
         <v>3.7526078187898708E-3</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
+      <c r="A23" s="10">
         <v>0.1</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="8">
         <f>B5*LN(1+B7*A23)+B6*LN(1-A23)</f>
         <v>5.0083668463568945E-3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
+      <c r="A24" s="10">
         <v>0.15</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="8">
         <f>B5*LN(1+B7*A24)+B6*LN(1-A24)</f>
         <v>3.7355500323385249E-3</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="14">
+      <c r="A25" s="10">
         <v>0.2</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="8">
         <f>B5*LN(1+B7*A25)+B6*LN(1-A25)</f>
         <v>-1.3774185471931988E-4</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
+      <c r="A26" s="10">
         <v>0.25</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="8">
         <f>B5*LN(1+B7*A26)+B6*LN(1-A26)</f>
         <v>-6.7279793804860266E-3</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="14">
+      <c r="A27" s="10">
         <v>0.3</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="8">
         <f>B5*LN(1+B7*A27)+B6*LN(1-A27)</f>
         <v>-1.6203379315309491E-2</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="14">
+      <c r="A28" s="10">
         <v>0.35</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="8">
         <f>B5*LN(1+B7*A28)+B6*LN(1-A28)</f>
         <v>-2.8794786393918387E-2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="14">
+      <c r="A29" s="10">
         <v>0.4</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="8">
         <f>B5*LN(1+B7*A29)+B6*LN(1-A29)</f>
         <v>-4.4811800553028691E-2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
+      <c r="A30" s="10">
         <v>0.45</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="8">
         <f>B5*LN(1+B7*A30)+B6*LN(1-A30)</f>
         <v>-6.4666694302163485E-2</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
+      <c r="A31" s="10">
         <v>0.5</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="8">
         <f>B5*LN(1+B7*A31)+B6*LN(1-A31)</f>
         <v>-8.8910421792484956E-2</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
+      <c r="A32" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="8">
         <f>B5*LN(1+B7*A32)+B6*LN(1-A32)</f>
         <v>-0.11828825128586179</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="14">
+      <c r="A33" s="10">
         <v>0.6</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="8">
         <f>B5*LN(1+B7*A33)+B6*LN(1-A33)</f>
         <v>-0.15382883325821511</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
+      <c r="A34" s="10">
         <v>0.65</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="8">
         <f>B5*LN(1+B7*A34)+B6*LN(1-A34)</f>
         <v>-0.19699354767253596</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="14">
+      <c r="A35" s="10">
         <v>0.7</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="8">
         <f>B5*LN(1+B7*A35)+B6*LN(1-A35)</f>
         <v>-0.24994222386247739</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
+      <c r="A36" s="10">
         <v>0.75</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="8">
         <f>B5*LN(1+B7*A36)+B6*LN(1-A36)</f>
         <v>-0.31604377913946824</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="14">
+      <c r="A37" s="10">
         <v>0.8</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="8">
         <f>B5*LN(1+B7*A37)+B6*LN(1-A37)</f>
         <v>-0.40096439489917968</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
+      <c r="A38" s="10">
         <v>0.85</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="8">
         <f>B5*LN(1+B7*A38)+B6*LN(1-A38)</f>
         <v>-0.51535189169901796</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="14">
+      <c r="A39" s="10">
         <v>0.9</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="8">
         <f>B5*LN(1+B7*A39)+B6*LN(1-A39)</f>
         <v>-0.68314365445250336</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="12">
         <v>0.5</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="12">
         <v>1</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="12">
         <v>1.5</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="12">
         <v>2</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="12">
         <v>3</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="17">
+      <c r="A44" s="13">
         <v>0.3</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="4">
         <f t="shared" ref="B44:G52" si="0">MAX((B$43*$A44-(1-$A44))/B$43,0)</f>
         <v>0</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="4">
         <f t="shared" si="0"/>
         <v>6.6666666666666652E-2</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="4">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="17">
+      <c r="A45" s="13">
         <v>0.35</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="4">
         <f t="shared" si="0"/>
         <v>2.4999999999999967E-2</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="4">
         <f t="shared" si="0"/>
         <v>0.13333333333333328</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="4">
         <f t="shared" si="0"/>
         <v>0.18749999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="17">
+      <c r="A46" s="13">
         <v>0.4</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="4">
         <f t="shared" si="0"/>
         <v>7.4014868308343765E-17</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="4">
         <f t="shared" si="0"/>
         <v>0.10000000000000003</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="4">
         <f t="shared" si="0"/>
         <v>0.20000000000000007</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="4">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="17">
+      <c r="A47" s="13">
         <v>0.45</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="4">
         <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="4">
         <f t="shared" si="0"/>
         <v>0.17499999999999999</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="4">
         <f t="shared" si="0"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="4">
         <f t="shared" si="0"/>
         <v>0.3125</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="17">
+      <c r="A48" s="13">
         <v>0.5</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="4">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="4">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="4">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="4">
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="17">
+      <c r="A49" s="13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="4">
         <f t="shared" si="0"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="4">
         <f t="shared" si="0"/>
         <v>0.25000000000000006</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="4">
         <f t="shared" si="0"/>
         <v>0.32500000000000007</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="4">
         <f t="shared" si="0"/>
         <v>0.40000000000000008</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="4">
         <f t="shared" si="0"/>
         <v>0.43750000000000006</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="17">
+      <c r="A50" s="13">
         <v>0.6</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="4">
         <f t="shared" si="0"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="4">
         <f t="shared" si="0"/>
         <v>0.33333333333333326</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="4">
         <f t="shared" si="0"/>
         <v>0.39999999999999997</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="4">
         <f t="shared" si="0"/>
         <v>0.46666666666666662</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="4">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="17">
+      <c r="A51" s="13">
         <v>0.65</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="4">
         <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="4">
         <f t="shared" si="0"/>
         <v>0.41666666666666674</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="4">
         <f t="shared" si="0"/>
         <v>0.47500000000000003</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="4">
         <f t="shared" si="0"/>
         <v>0.53333333333333333</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="4">
         <f t="shared" si="0"/>
         <v>0.5625</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+      <c r="A52" s="13">
         <v>0.7</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="4">
         <f t="shared" si="0"/>
         <v>9.9999999999999867E-2</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="4">
         <f t="shared" si="0"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="4">
         <f t="shared" si="0"/>
         <v>0.49999999999999983</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="4">
         <f t="shared" si="0"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="4">
         <f t="shared" si="0"/>
         <v>0.59999999999999987</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="4">
         <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1682,4 +1748,123 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309A2133-BCDD-4B63-9E7C-62AB85B494DC}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.42578125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="16" style="19" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0.08</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G8" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C9" s="21">
+        <f ca="1">_xlfn.NORM.INV(RAND(),$C$5,$C$6)</f>
+        <v>0.11810258510857319</v>
+      </c>
+      <c r="D9" s="19">
+        <f ca="1">_xlfn.NORM.INV(RAND(),C5,C6)</f>
+        <v>6.3725193522821688E-2</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C10" s="21">
+        <f ca="1">_xlfn.NORM.INV(RAND(),$C$5,$C$6)</f>
+        <v>8.0051962391997758E-2</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C11" s="21">
+        <f ca="1">_xlfn.NORM.INV(RAND(),$C$5,$C$6)</f>
+        <v>9.1088786404253164E-2</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C12" s="21">
+        <f ca="1">_xlfn.NORM.INV(RAND(),$C$5,$C$6)</f>
+        <v>0.11337631698414151</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C13" s="21">
+        <f t="shared" ref="C13:C14" ca="1" si="0">_xlfn.NORM.INV(RAND(),$C$5,$C$6)</f>
+        <v>0.10317158956313018</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C14" s="21">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.11435334133734129</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C15" s="21">
+        <f ca="1">_xlfn.NORM.INV(RAND(),$C$5,$C$6)</f>
+        <v>8.4371823240023264E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>